--- a/documents/PROJECT_TRACKER.xlsx
+++ b/documents/PROJECT_TRACKER.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="27">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,8 +174,24 @@
       <color rgb="FF374151"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -300,8 +318,32 @@
         <fgColor rgb="FF6B7280"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -323,11 +365,55 @@
         <color rgb="FFD1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -501,6 +587,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +996,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Q2–Q4 2026  |  MVP → v1.5 → v2.0  |  Last Updated: April 2026</t>
+          <t>Q2–Q4 2026  |  MVP → v1.5 → v2.0  |  Last Updated: April 6, 2026</t>
         </is>
       </c>
     </row>
@@ -946,7 +1049,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Phase 0 — Foundation</t>
         </is>
@@ -961,23 +1064,23 @@
           <t>M1: Foundation</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="67" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="67" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0</v>
+      <c r="J6" s="71" t="n">
+        <v>91.67</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1263,6 +1366,12 @@
           <t>Task completed</t>
         </is>
       </c>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="66" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="inlineStr">
@@ -1275,6 +1384,12 @@
           <t>Work underway</t>
         </is>
       </c>
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="65" t="n"/>
+      <c r="H23" s="65" t="n"/>
+      <c r="I23" s="66" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="inlineStr">
@@ -1287,6 +1402,12 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="D24" s="65" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="65" t="n"/>
+      <c r="H24" s="65" t="n"/>
+      <c r="I24" s="66" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="16" t="inlineStr">
@@ -1299,6 +1420,12 @@
           <t>Dependency/external</t>
         </is>
       </c>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="65" t="n"/>
+      <c r="H25" s="65" t="n"/>
+      <c r="I25" s="66" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
@@ -1311,6 +1438,12 @@
           <t>Blocked issue</t>
         </is>
       </c>
+      <c r="D26" s="65" t="n"/>
+      <c r="E26" s="65" t="n"/>
+      <c r="F26" s="65" t="n"/>
+      <c r="G26" s="65" t="n"/>
+      <c r="H26" s="65" t="n"/>
+      <c r="I26" s="66" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="17" t="inlineStr">
@@ -1323,6 +1456,12 @@
           <t>Must for milestone</t>
         </is>
       </c>
+      <c r="D27" s="65" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="65" t="n"/>
+      <c r="G27" s="65" t="n"/>
+      <c r="H27" s="65" t="n"/>
+      <c r="I27" s="66" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
@@ -1335,6 +1474,12 @@
           <t>Important</t>
         </is>
       </c>
+      <c r="D28" s="65" t="n"/>
+      <c r="E28" s="65" t="n"/>
+      <c r="F28" s="65" t="n"/>
+      <c r="G28" s="65" t="n"/>
+      <c r="H28" s="65" t="n"/>
+      <c r="I28" s="66" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
@@ -1347,6 +1492,12 @@
           <t>Nice-to-have</t>
         </is>
       </c>
+      <c r="D29" s="65" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="65" t="n"/>
+      <c r="G29" s="65" t="n"/>
+      <c r="H29" s="65" t="n"/>
+      <c r="I29" s="66" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1522,9 +1673,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H7" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I7" s="27" t="inlineStr"/>
@@ -1573,9 +1724,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H8" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I8" s="27" t="inlineStr"/>
@@ -1624,9 +1775,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H9" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I9" s="27" t="inlineStr"/>
@@ -1675,9 +1826,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H10" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr"/>
@@ -1726,9 +1877,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H11" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I11" s="27" t="inlineStr"/>
@@ -1777,9 +1928,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H12" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr"/>
@@ -1828,9 +1979,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H13" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr"/>
@@ -1879,9 +2030,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H14" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr"/>
@@ -1930,9 +2081,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H15" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr"/>
@@ -1981,9 +2132,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H16" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr"/>
@@ -2032,9 +2183,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="H17" s="67" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I17" s="27" t="inlineStr"/>
@@ -2083,7 +2234,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="68" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/documents/PROJECT_TRACKER.xlsx
+++ b/documents/PROJECT_TRACKER.xlsx
@@ -996,7 +996,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Q2–Q4 2026  |  MVP → v1.5 → v2.0  |  Last Updated: April 6, 2026</t>
+          <t>Q2-Q4 2026  |  MVP to v1.5 to v2.0  |  Last Updated: 2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1103,19 @@
         <v>37</v>
       </c>
       <c r="F7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>37</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2316,12 +2316,16 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr"/>
       <c r="J21" s="27" t="inlineStr"/>
-      <c r="K21" s="28" t="inlineStr"/>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L21" s="29" t="inlineStr"/>
       <c r="M21" s="24" t="inlineStr">
         <is>
@@ -2367,12 +2371,16 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr"/>
       <c r="J22" s="27" t="inlineStr"/>
-      <c r="K22" s="28" t="inlineStr"/>
+      <c r="K22" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L22" s="29" t="inlineStr"/>
       <c r="M22" s="24" t="inlineStr">
         <is>
@@ -2418,12 +2426,16 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I23" s="27" t="inlineStr"/>
       <c r="J23" s="27" t="inlineStr"/>
-      <c r="K23" s="28" t="inlineStr"/>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L23" s="29" t="inlineStr"/>
       <c r="M23" s="24" t="inlineStr">
         <is>
@@ -2469,12 +2481,16 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr"/>
       <c r="J24" s="27" t="inlineStr"/>
-      <c r="K24" s="28" t="inlineStr"/>
+      <c r="K24" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L24" s="29" t="inlineStr"/>
       <c r="M24" s="24" t="inlineStr">
         <is>
@@ -2520,12 +2536,16 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I25" s="27" t="inlineStr"/>
       <c r="J25" s="27" t="inlineStr"/>
-      <c r="K25" s="28" t="inlineStr"/>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L25" s="29" t="inlineStr"/>
       <c r="M25" s="24" t="inlineStr">
         <is>
@@ -2571,12 +2591,16 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I26" s="27" t="inlineStr"/>
       <c r="J26" s="27" t="inlineStr"/>
-      <c r="K26" s="28" t="inlineStr"/>
+      <c r="K26" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L26" s="29" t="inlineStr"/>
       <c r="M26" s="24" t="inlineStr">
         <is>
@@ -2622,12 +2646,16 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I27" s="27" t="inlineStr"/>
       <c r="J27" s="27" t="inlineStr"/>
-      <c r="K27" s="28" t="inlineStr"/>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L27" s="29" t="inlineStr"/>
       <c r="M27" s="24" t="inlineStr">
         <is>
@@ -2673,12 +2701,16 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr"/>
       <c r="J28" s="27" t="inlineStr"/>
-      <c r="K28" s="28" t="inlineStr"/>
+      <c r="K28" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L28" s="29" t="inlineStr"/>
       <c r="M28" s="24" t="inlineStr">
         <is>
@@ -2724,12 +2756,16 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I29" s="27" t="inlineStr"/>
       <c r="J29" s="27" t="inlineStr"/>
-      <c r="K29" s="28" t="inlineStr"/>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L29" s="29" t="inlineStr"/>
       <c r="M29" s="24" t="inlineStr">
         <is>
@@ -2775,12 +2811,16 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr"/>
       <c r="J30" s="27" t="inlineStr"/>
-      <c r="K30" s="28" t="inlineStr"/>
+      <c r="K30" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L30" s="29" t="inlineStr"/>
       <c r="M30" s="24" t="inlineStr">
         <is>
@@ -2826,12 +2866,16 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I31" s="27" t="inlineStr"/>
       <c r="J31" s="27" t="inlineStr"/>
-      <c r="K31" s="28" t="inlineStr"/>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L31" s="29" t="inlineStr"/>
       <c r="M31" s="24" t="inlineStr">
         <is>
@@ -2877,12 +2921,16 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr"/>
       <c r="J32" s="27" t="inlineStr"/>
-      <c r="K32" s="28" t="inlineStr"/>
+      <c r="K32" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L32" s="29" t="inlineStr"/>
       <c r="M32" s="24" t="inlineStr">
         <is>
@@ -2928,12 +2976,16 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I33" s="27" t="inlineStr"/>
       <c r="J33" s="27" t="inlineStr"/>
-      <c r="K33" s="28" t="inlineStr"/>
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L33" s="29" t="inlineStr"/>
       <c r="M33" s="24" t="inlineStr">
         <is>
@@ -2979,12 +3031,16 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr"/>
       <c r="J34" s="27" t="inlineStr"/>
-      <c r="K34" s="28" t="inlineStr"/>
+      <c r="K34" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L34" s="29" t="inlineStr"/>
       <c r="M34" s="24" t="inlineStr">
         <is>
@@ -3030,12 +3086,16 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr"/>
       <c r="J35" s="27" t="inlineStr"/>
-      <c r="K35" s="28" t="inlineStr"/>
+      <c r="K35" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L35" s="29" t="inlineStr"/>
       <c r="M35" s="24" t="inlineStr">
         <is>
@@ -3081,12 +3141,16 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr"/>
       <c r="J36" s="27" t="inlineStr"/>
-      <c r="K36" s="28" t="inlineStr"/>
+      <c r="K36" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L36" s="29" t="inlineStr"/>
       <c r="M36" s="24" t="inlineStr">
         <is>
@@ -3132,12 +3196,16 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr"/>
       <c r="J37" s="27" t="inlineStr"/>
-      <c r="K37" s="28" t="inlineStr"/>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L37" s="29" t="inlineStr"/>
       <c r="M37" s="24" t="inlineStr">
         <is>
@@ -3183,12 +3251,16 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I38" s="27" t="inlineStr"/>
       <c r="J38" s="27" t="inlineStr"/>
-      <c r="K38" s="28" t="inlineStr"/>
+      <c r="K38" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L38" s="29" t="inlineStr"/>
       <c r="M38" s="24" t="inlineStr">
         <is>
@@ -3234,12 +3306,16 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr"/>
       <c r="J39" s="27" t="inlineStr"/>
-      <c r="K39" s="28" t="inlineStr"/>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L39" s="29" t="inlineStr"/>
       <c r="M39" s="24" t="inlineStr">
         <is>
@@ -3285,12 +3361,16 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I40" s="27" t="inlineStr"/>
       <c r="J40" s="27" t="inlineStr"/>
-      <c r="K40" s="28" t="inlineStr"/>
+      <c r="K40" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L40" s="29" t="inlineStr"/>
       <c r="M40" s="24" t="inlineStr">
         <is>
@@ -3336,12 +3416,16 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr"/>
       <c r="J41" s="27" t="inlineStr"/>
-      <c r="K41" s="28" t="inlineStr"/>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L41" s="29" t="inlineStr"/>
       <c r="M41" s="24" t="inlineStr">
         <is>
@@ -3387,12 +3471,16 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I42" s="27" t="inlineStr"/>
       <c r="J42" s="27" t="inlineStr"/>
-      <c r="K42" s="28" t="inlineStr"/>
+      <c r="K42" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L42" s="29" t="inlineStr"/>
       <c r="M42" s="24" t="inlineStr">
         <is>
@@ -3438,12 +3526,16 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr"/>
       <c r="J43" s="27" t="inlineStr"/>
-      <c r="K43" s="28" t="inlineStr"/>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L43" s="29" t="inlineStr"/>
       <c r="M43" s="24" t="inlineStr">
         <is>
@@ -3489,12 +3581,16 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I44" s="27" t="inlineStr"/>
       <c r="J44" s="27" t="inlineStr"/>
-      <c r="K44" s="28" t="inlineStr"/>
+      <c r="K44" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L44" s="29" t="inlineStr"/>
       <c r="M44" s="24" t="inlineStr">
         <is>
@@ -3540,12 +3636,16 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I45" s="27" t="inlineStr"/>
       <c r="J45" s="27" t="inlineStr"/>
-      <c r="K45" s="28" t="inlineStr"/>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="L45" s="29" t="inlineStr"/>
       <c r="M45" s="24" t="inlineStr">
         <is>
@@ -3591,7 +3691,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I46" s="27" t="inlineStr"/>
@@ -3642,7 +3742,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr"/>
@@ -3693,7 +3793,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I48" s="27" t="inlineStr"/>
@@ -3744,7 +3844,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr"/>
@@ -3795,7 +3895,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr"/>
@@ -3846,7 +3946,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr"/>
@@ -3897,7 +3997,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I52" s="27" t="inlineStr"/>
@@ -3948,7 +4048,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr"/>
@@ -3999,7 +4099,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I54" s="27" t="inlineStr"/>
@@ -4050,7 +4150,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr"/>
@@ -4101,7 +4201,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I56" s="27" t="inlineStr"/>
@@ -4152,7 +4252,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr"/>

--- a/documents/PROJECT_TRACKER.xlsx
+++ b/documents/PROJECT_TRACKER.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -190,8 +190,17 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <color rgb="00375623"/>
+    </font>
+    <font>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <color rgb="001F497D"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -342,6 +351,12 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -413,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -605,6 +620,15 @@
     </xf>
     <xf numFmtId="164" fontId="27" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -996,7 +1020,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Q2-Q4 2026  |  MVP to v1.5 to v2.0  |  Last Updated: 2026-04-09</t>
+          <t>Q2-Q4 2026  |  MVP to v1.5 to v2.0  |  Last Updated: 2026-04-10</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="71" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1103,10 +1127,10 @@
         <v>37</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -1115,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1673,7 +1697,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H7" s="67" t="inlineStr">
+      <c r="H7" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1724,7 +1748,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H8" s="67" t="inlineStr">
+      <c r="H8" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1775,7 +1799,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H9" s="67" t="inlineStr">
+      <c r="H9" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1826,7 +1850,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H10" s="67" t="inlineStr">
+      <c r="H10" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1877,7 +1901,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H11" s="67" t="inlineStr">
+      <c r="H11" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1928,7 +1952,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H12" s="67" t="inlineStr">
+      <c r="H12" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1979,7 +2003,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H13" s="67" t="inlineStr">
+      <c r="H13" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2030,7 +2054,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H14" s="67" t="inlineStr">
+      <c r="H14" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2081,7 +2105,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H15" s="67" t="inlineStr">
+      <c r="H15" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2132,7 +2156,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H16" s="67" t="inlineStr">
+      <c r="H16" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2183,7 +2207,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="67" t="inlineStr">
+      <c r="H17" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2234,7 +2258,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="68" t="inlineStr">
+      <c r="H18" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2314,7 +2338,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2333,7 +2357,11 @@
         </is>
       </c>
       <c r="N21" s="24" t="inlineStr"/>
-      <c r="O21" s="27" t="inlineStr"/>
+      <c r="O21" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -2369,7 +2397,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2388,7 +2416,11 @@
         </is>
       </c>
       <c r="N22" s="24" t="inlineStr"/>
-      <c r="O22" s="27" t="inlineStr"/>
+      <c r="O22" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="10" t="n">
@@ -2424,7 +2456,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2443,7 +2475,11 @@
         </is>
       </c>
       <c r="N23" s="24" t="inlineStr"/>
-      <c r="O23" s="27" t="inlineStr"/>
+      <c r="O23" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="10" t="n">
@@ -2479,7 +2515,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2498,7 +2534,11 @@
         </is>
       </c>
       <c r="N24" s="24" t="inlineStr"/>
-      <c r="O24" s="27" t="inlineStr"/>
+      <c r="O24" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="10" t="n">
@@ -2534,7 +2574,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2553,7 +2593,11 @@
         </is>
       </c>
       <c r="N25" s="24" t="inlineStr"/>
-      <c r="O25" s="27" t="inlineStr"/>
+      <c r="O25" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="10" t="n">
@@ -2589,7 +2633,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2608,7 +2652,11 @@
         </is>
       </c>
       <c r="N26" s="24" t="inlineStr"/>
-      <c r="O26" s="27" t="inlineStr"/>
+      <c r="O26" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="10" t="n">
@@ -2644,7 +2692,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2663,7 +2711,11 @@
         </is>
       </c>
       <c r="N27" s="24" t="inlineStr"/>
-      <c r="O27" s="27" t="inlineStr"/>
+      <c r="O27" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="10" t="n">
@@ -2699,7 +2751,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2718,7 +2770,11 @@
         </is>
       </c>
       <c r="N28" s="24" t="inlineStr"/>
-      <c r="O28" s="27" t="inlineStr"/>
+      <c r="O28" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="10" t="n">
@@ -2754,7 +2810,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2773,7 +2829,11 @@
         </is>
       </c>
       <c r="N29" s="24" t="inlineStr"/>
-      <c r="O29" s="27" t="inlineStr"/>
+      <c r="O29" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="10" t="n">
@@ -2809,7 +2869,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2828,7 +2888,11 @@
         </is>
       </c>
       <c r="N30" s="24" t="inlineStr"/>
-      <c r="O30" s="27" t="inlineStr"/>
+      <c r="O30" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="10" t="n">
@@ -2864,7 +2928,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2883,7 +2947,11 @@
         </is>
       </c>
       <c r="N31" s="24" t="inlineStr"/>
-      <c r="O31" s="27" t="inlineStr"/>
+      <c r="O31" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="10" t="n">
@@ -2919,7 +2987,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2938,7 +3006,11 @@
         </is>
       </c>
       <c r="N32" s="24" t="inlineStr"/>
-      <c r="O32" s="27" t="inlineStr"/>
+      <c r="O32" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="10" t="n">
@@ -2974,7 +3046,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2993,7 +3065,11 @@
         </is>
       </c>
       <c r="N33" s="24" t="inlineStr"/>
-      <c r="O33" s="27" t="inlineStr"/>
+      <c r="O33" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="10" t="n">
@@ -3029,7 +3105,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3048,7 +3124,11 @@
         </is>
       </c>
       <c r="N34" s="24" t="inlineStr"/>
-      <c r="O34" s="27" t="inlineStr"/>
+      <c r="O34" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="10" t="n">
@@ -3084,7 +3164,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3103,7 +3183,11 @@
         </is>
       </c>
       <c r="N35" s="24" t="inlineStr"/>
-      <c r="O35" s="27" t="inlineStr"/>
+      <c r="O35" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="10" t="n">
@@ -3139,7 +3223,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3158,7 +3242,11 @@
         </is>
       </c>
       <c r="N36" s="24" t="inlineStr"/>
-      <c r="O36" s="27" t="inlineStr"/>
+      <c r="O36" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="10" t="n">
@@ -3194,7 +3282,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3213,7 +3301,11 @@
         </is>
       </c>
       <c r="N37" s="24" t="inlineStr"/>
-      <c r="O37" s="27" t="inlineStr"/>
+      <c r="O37" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="10" t="n">
@@ -3249,7 +3341,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3268,7 +3360,11 @@
         </is>
       </c>
       <c r="N38" s="24" t="inlineStr"/>
-      <c r="O38" s="27" t="inlineStr"/>
+      <c r="O38" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="10" t="n">
@@ -3304,7 +3400,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3323,7 +3419,11 @@
         </is>
       </c>
       <c r="N39" s="24" t="inlineStr"/>
-      <c r="O39" s="27" t="inlineStr"/>
+      <c r="O39" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="10" t="n">
@@ -3359,7 +3459,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3377,8 +3477,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N40" s="24" t="inlineStr"/>
-      <c r="O40" s="27" t="inlineStr"/>
+      <c r="N40" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O40" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="10" t="n">
@@ -3414,7 +3522,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3432,8 +3540,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N41" s="24" t="inlineStr"/>
-      <c r="O41" s="27" t="inlineStr"/>
+      <c r="N41" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O41" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="10" t="n">
@@ -3469,7 +3585,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3487,8 +3603,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N42" s="24" t="inlineStr"/>
-      <c r="O42" s="27" t="inlineStr"/>
+      <c r="N42" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O42" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="10" t="n">
@@ -3524,7 +3648,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H43" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3542,8 +3666,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N43" s="24" t="inlineStr"/>
-      <c r="O43" s="27" t="inlineStr"/>
+      <c r="N43" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O43" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="10" t="n">
@@ -3579,7 +3711,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3597,8 +3729,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N44" s="24" t="inlineStr"/>
-      <c r="O44" s="27" t="inlineStr"/>
+      <c r="N44" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O44" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="10" t="n">
@@ -3634,7 +3774,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="72" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3652,8 +3792,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N45" s="24" t="inlineStr"/>
-      <c r="O45" s="27" t="inlineStr"/>
+      <c r="N45" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O45" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="10" t="n">
@@ -3689,9 +3837,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H46" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I46" s="27" t="inlineStr"/>
@@ -3703,8 +3851,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N46" s="24" t="inlineStr"/>
-      <c r="O46" s="27" t="inlineStr"/>
+      <c r="N46" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O46" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="10" t="n">
@@ -3740,9 +3896,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H47" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr"/>
@@ -3754,8 +3910,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N47" s="24" t="inlineStr"/>
-      <c r="O47" s="27" t="inlineStr"/>
+      <c r="N47" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O47" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="10" t="n">
@@ -3791,9 +3955,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I48" s="27" t="inlineStr"/>
@@ -3805,8 +3969,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N48" s="24" t="inlineStr"/>
-      <c r="O48" s="27" t="inlineStr"/>
+      <c r="N48" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O48" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="10" t="n">
@@ -3842,9 +4014,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H49" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr"/>
@@ -3856,8 +4028,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N49" s="24" t="inlineStr"/>
-      <c r="O49" s="27" t="inlineStr"/>
+      <c r="N49" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O49" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="10" t="n">
@@ -3893,9 +4073,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H50" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr"/>
@@ -3907,8 +4087,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N50" s="24" t="inlineStr"/>
-      <c r="O50" s="27" t="inlineStr"/>
+      <c r="N50" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O50" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="10" t="n">
@@ -3944,9 +4132,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H51" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr"/>
@@ -3958,8 +4146,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N51" s="24" t="inlineStr"/>
-      <c r="O51" s="27" t="inlineStr"/>
+      <c r="N51" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O51" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="10" t="n">
@@ -3995,9 +4191,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H52" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I52" s="27" t="inlineStr"/>
@@ -4009,8 +4205,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N52" s="24" t="inlineStr"/>
-      <c r="O52" s="27" t="inlineStr"/>
+      <c r="N52" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O52" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="10" t="n">
@@ -4046,9 +4250,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H53" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr"/>
@@ -4060,8 +4264,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N53" s="24" t="inlineStr"/>
-      <c r="O53" s="27" t="inlineStr"/>
+      <c r="N53" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O53" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="10" t="n">
@@ -4097,9 +4309,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H54" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I54" s="27" t="inlineStr"/>
@@ -4111,8 +4323,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N54" s="24" t="inlineStr"/>
-      <c r="O54" s="27" t="inlineStr"/>
+      <c r="N54" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O54" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="10" t="n">
@@ -4148,9 +4368,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H55" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr"/>
@@ -4162,8 +4382,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N55" s="24" t="inlineStr"/>
-      <c r="O55" s="27" t="inlineStr"/>
+      <c r="N55" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O55" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="10" t="n">
@@ -4199,9 +4427,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H56" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I56" s="27" t="inlineStr"/>
@@ -4213,8 +4441,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N56" s="24" t="inlineStr"/>
-      <c r="O56" s="27" t="inlineStr"/>
+      <c r="N56" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O56" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="10" t="n">
@@ -4250,9 +4486,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H57" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr"/>
@@ -4264,8 +4500,16 @@
           <t>M2: Alpha</t>
         </is>
       </c>
-      <c r="N57" s="24" t="inlineStr"/>
-      <c r="O57" s="27" t="inlineStr"/>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>Frontend wiring complete — 0 build errors, 2026-04-10</t>
+        </is>
+      </c>
+      <c r="O57" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="36" t="inlineStr">
@@ -4330,7 +4574,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4381,7 +4625,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4432,7 +4676,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4483,7 +4727,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4534,7 +4778,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4585,7 +4829,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H65" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4636,7 +4880,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4687,7 +4931,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H67" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4738,7 +4982,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4789,7 +5033,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4840,7 +5084,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H70" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4891,7 +5135,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H71" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4942,7 +5186,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H72" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4993,7 +5237,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H73" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5044,7 +5288,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H74" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5095,7 +5339,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H75" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5146,7 +5390,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H76" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5197,7 +5441,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H77" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5248,7 +5492,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H78" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5299,7 +5543,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H79" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5350,7 +5594,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H80" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5430,7 +5674,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="H83" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5481,7 +5725,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5532,7 +5776,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H85" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5583,7 +5827,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="H86" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5634,7 +5878,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H87" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5685,7 +5929,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H88" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5736,7 +5980,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H89" s="10" t="inlineStr">
+      <c r="H89" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5787,7 +6031,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
+      <c r="H90" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5838,7 +6082,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H91" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5889,7 +6133,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H92" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5940,7 +6184,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H93" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5991,7 +6235,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6042,7 +6286,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H95" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6093,7 +6337,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H96" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6144,7 +6388,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H97" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6195,7 +6439,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H98" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6246,7 +6490,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H99" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6297,7 +6541,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H100" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6348,7 +6592,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6428,7 +6672,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6479,7 +6723,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H105" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6530,7 +6774,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="H106" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6581,7 +6825,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
+      <c r="H107" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6632,7 +6876,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6683,7 +6927,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H109" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6734,7 +6978,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H110" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6785,7 +7029,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="H111" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6836,7 +7080,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H112" s="10" t="inlineStr">
+      <c r="H112" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6887,7 +7131,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H113" s="10" t="inlineStr">
+      <c r="H113" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6938,7 +7182,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H114" s="10" t="inlineStr">
+      <c r="H114" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6989,7 +7233,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H115" s="10" t="inlineStr">
+      <c r="H115" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7040,7 +7284,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="H116" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7091,7 +7335,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H117" s="10" t="inlineStr">
+      <c r="H117" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7142,7 +7386,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H118" s="10" t="inlineStr">
+      <c r="H118" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7193,7 +7437,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H119" s="10" t="inlineStr">
+      <c r="H119" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7244,7 +7488,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H120" s="10" t="inlineStr">
+      <c r="H120" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7295,7 +7539,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H121" s="10" t="inlineStr">
+      <c r="H121" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7346,7 +7590,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H122" s="10" t="inlineStr">
+      <c r="H122" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7397,7 +7641,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H123" s="10" t="inlineStr">
+      <c r="H123" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7448,7 +7692,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H124" s="10" t="inlineStr">
+      <c r="H124" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7499,7 +7743,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H125" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7550,7 +7794,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H126" s="10" t="inlineStr">
+      <c r="H126" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7601,7 +7845,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H127" s="10" t="inlineStr">
+      <c r="H127" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7652,7 +7896,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H128" s="10" t="inlineStr">
+      <c r="H128" s="73" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
